--- a/informed_consent_forms/015_smart_infrastructure_testing_consent_form--informed_consent_forms.xlsx
+++ b/informed_consent_forms/015_smart_infrastructure_testing_consent_form--informed_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1203,29 +1203,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>i_am_a_participant_in_this_testing_project.</t>
+          <t>i_am_not_a_participant_in_this_testing_project.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>I am a participant in this testing project.</t>
+          <t>I am not a participant in this testing project.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>participant_consent_choices</t>
+          <t>observer_consent_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>i_am_not_a_participant_in_this_testing_project.</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>I am not a participant in this testing project.</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>observer_consent_choices</t>
+          <t>participant_contract_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>participant_agreement_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Participant Agreement 1</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_agreement_1</t>
+          <t>participant_agreement_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Participant Agreement 1</t>
+          <t>Participant Agreement 2</t>
         </is>
       </c>
     </row>
@@ -1288,29 +1288,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>participant_agreement_2</t>
+          <t>participant_agreement_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Participant Agreement 2</t>
+          <t>Participant Agreement 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>participant_contract_choices</t>
+          <t>participant_gender_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>participant_agreement_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Participant Agreement 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1322,27 +1322,10 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>participant_gender_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
